--- a/apps/sheets/tests/fixtures/xlsx/budget.xlsx
+++ b/apps/sheets/tests/fixtures/xlsx/budget.xlsx
@@ -81,6 +81,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -180,6 +193,20 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C3">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 

--- a/apps/sheets/tests/fixtures/xlsx/budget.xlsx
+++ b/apps/sheets/tests/fixtures/xlsx/budget.xlsx
@@ -72,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment horizontal="center"/>
@@ -80,6 +80,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
   </cellXfs>
   <dxfs count="1">
     <dxf>
@@ -212,6 +218,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -220,6 +227,20 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Everything in this column is written across several lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Sideways</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/apps/sheets/tests/fixtures/xlsx/budget.xlsx
+++ b/apps/sheets/tests/fixtures/xlsx/budget.xlsx
@@ -103,6 +103,160 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Budget!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Spent</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Budget!$A$2:$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Budget!$B$2:$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1234.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="1"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Spending by month"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="914400" cy="914400"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -157,63 +311,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-  </cols>
-  <mergeCells count="1">
-    <mergeCell ref="B1:C1"/>
-  </mergeCells>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1234.5</v>
-      </c>
-      <c r="C2" s="3">
-        <v>45292</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>-99</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.155</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B2:B3">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C3">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-</worksheet>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><dimension ref="A1:C4"/><sheetFormatPr defaultRowHeight="15"/><cols><col min="1" max="1" width="20" customWidth="1"/></cols><mergeCells count="1"><mergeCell ref="B1:C1"/></mergeCells><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s" s="1"><v>1</v></c></row><row r="2" ht="30" customHeight="1"><c r="A2" t="s"><v>2</v></c><c r="B2" s="2"><v>1234.5</v></c><c r="C2" s="3"><v>45292</v></c></row><row r="3"><c r="A3" t="s"><v>3</v></c><c r="B3" s="2"><v>-99</v></c><c r="C3" s="4"><v>0.155</v></c></row></sheetData><conditionalFormatting sqref="B2:B3"><cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan"><formula>0</formula></cfRule></conditionalFormatting><conditionalFormatting sqref="C3:C3"><cfRule type="dataBar" priority="2"><dataBar><cfvo type="min"/><cfvo type="max"/><color rgb="FF638EC6"/></dataBar></cfRule></conditionalFormatting><drawing r:id="rId1"/></worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/apps/sheets/tests/fixtures/xlsx/budget.xlsx
+++ b/apps/sheets/tests/fixtures/xlsx/budget.xlsx
@@ -10,6 +10,37 @@
     <sheet name="Working" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>tc=Olena</author>
+    <author>Dmytro</author>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <t>Olena:</t>
+        </r>
+        <r>
+          <t xml:space="preserve"> Is this the refund?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="1">
+      <text>
+        <r>
+          <t>Dmytro:</t>
+        </r>
+        <r>
+          <t xml:space="preserve"> Start of the year.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -257,6 +288,13 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <person displayName="Olena" id="{P1}" userId="olena"/>
+  <person displayName="Dmytro" id="{P2}" userId="dmytro"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -311,6 +349,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <threadedComment ref="B3" dT="2026-09-01T09:00:00Z" personId="{P1}" id="{C1}">
+    <text>Is this the refund?</text>
+  </threadedComment>
+  <threadedComment ref="B3" dT="2026-09-01T09:05:00Z" personId="{P2}" id="{C2}" parentId="{C1}">
+    <text>Yes, from March.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><dimension ref="A1:C4"/><sheetFormatPr defaultRowHeight="15"/><cols><col min="1" max="1" width="20" customWidth="1"/></cols><mergeCells count="1"><mergeCell ref="B1:C1"/></mergeCells><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s" s="1"><v>1</v></c></row><row r="2" ht="30" customHeight="1"><c r="A2" t="s"><v>2</v></c><c r="B2" s="2"><v>1234.5</v></c><c r="C2" s="3"><v>45292</v></c></row><row r="3"><c r="A3" t="s"><v>3</v></c><c r="B3" s="2"><v>-99</v></c><c r="C3" s="4"><v>0.155</v></c></row></sheetData><conditionalFormatting sqref="B2:B3"><cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan"><formula>0</formula></cfRule></conditionalFormatting><conditionalFormatting sqref="C3:C3"><cfRule type="dataBar" priority="2"><dataBar><cfvo type="min"/><cfvo type="max"/><color rgb="FF638EC6"/></dataBar></cfRule></conditionalFormatting><drawing r:id="rId1"/></worksheet>
 </file>
 

--- a/apps/sheets/tests/fixtures/xlsx/budget.xlsx
+++ b/apps/sheets/tests/fixtures/xlsx/budget.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Month</t>
   </si>
@@ -56,6 +56,18 @@
   </si>
   <si>
     <t>February</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Spent </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFC00000"/>
+      </rPr>
+      <t>so far</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -360,7 +372,7 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><dimension ref="A1:C4"/><sheetFormatPr defaultRowHeight="15"/><cols><col min="1" max="1" width="20" customWidth="1"/></cols><mergeCells count="1"><mergeCell ref="B1:C1"/></mergeCells><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s" s="1"><v>1</v></c></row><row r="2" ht="30" customHeight="1"><c r="A2" t="s"><v>2</v></c><c r="B2" s="2"><v>1234.5</v></c><c r="C2" s="3"><v>45292</v></c></row><row r="3"><c r="A3" t="s"><v>3</v></c><c r="B3" s="2"><v>-99</v></c><c r="C3" s="4"><v>0.155</v></c></row></sheetData><conditionalFormatting sqref="B2:B3"><cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan"><formula>0</formula></cfRule></conditionalFormatting><conditionalFormatting sqref="C3:C3"><cfRule type="dataBar" priority="2"><dataBar><cfvo type="min"/><cfvo type="max"/><color rgb="FF638EC6"/></dataBar></cfRule></conditionalFormatting><drawing r:id="rId1"/></worksheet>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><dimension ref="A1:C4"/><sheetFormatPr defaultRowHeight="15"/><cols><col min="1" max="1" width="20" customWidth="1"/></cols><mergeCells count="1"><mergeCell ref="B1:C1"/></mergeCells><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s" s="1"><v>1</v></c></row><row r="2" ht="30" customHeight="1"><c r="A2" t="s"><v>2</v></c><c r="B2" s="2"><v>1234.5</v></c><c r="C2" s="3"><v>45292</v></c></row><row r="3"><c r="A3" t="s"><v>3</v></c><c r="B3" s="2"><v>-99</v></c><c r="C3" s="4"><v>0.155</v></c></row><row r="4"><c r="A4" t="s"><v>4</v></c><c r="B4" t="inlineStr"><is><r><t xml:space="preserve">Net </t></r><r><rPr><i/></rPr><t>total</t></r></is></c></row></sheetData><conditionalFormatting sqref="B2:B3"><cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan"><formula>0</formula></cfRule></conditionalFormatting><conditionalFormatting sqref="C3:C3"><cfRule type="dataBar" priority="2"><dataBar><cfvo type="min"/><cfvo type="max"/><color rgb="FF638EC6"/></dataBar></cfRule></conditionalFormatting><drawing r:id="rId1"/></worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/apps/sheets/tests/fixtures/xlsx/budget.xlsx
+++ b/apps/sheets/tests/fixtures/xlsx/budget.xlsx
@@ -372,7 +372,7 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><dimension ref="A1:C4"/><sheetFormatPr defaultRowHeight="15"/><cols><col min="1" max="1" width="20" customWidth="1"/></cols><mergeCells count="1"><mergeCell ref="B1:C1"/></mergeCells><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s" s="1"><v>1</v></c></row><row r="2" ht="30" customHeight="1"><c r="A2" t="s"><v>2</v></c><c r="B2" s="2"><v>1234.5</v></c><c r="C2" s="3"><v>45292</v></c></row><row r="3"><c r="A3" t="s"><v>3</v></c><c r="B3" s="2"><v>-99</v></c><c r="C3" s="4"><v>0.155</v></c></row><row r="4"><c r="A4" t="s"><v>4</v></c><c r="B4" t="inlineStr"><is><r><t xml:space="preserve">Net </t></r><r><rPr><i/></rPr><t>total</t></r></is></c></row></sheetData><conditionalFormatting sqref="B2:B3"><cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan"><formula>0</formula></cfRule></conditionalFormatting><conditionalFormatting sqref="C3:C3"><cfRule type="dataBar" priority="2"><dataBar><cfvo type="min"/><cfvo type="max"/><color rgb="FF638EC6"/></dataBar></cfRule></conditionalFormatting><drawing r:id="rId1"/></worksheet>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><dimension ref="A1:C4"/><sheetFormatPr defaultRowHeight="15"/><cols><col min="1" max="1" width="20" customWidth="1"/></cols><mergeCells count="1"><mergeCell ref="B1:C1"/></mergeCells><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s" s="1"><v>1</v></c></row><row r="2" ht="30" customHeight="1"><c r="A2" t="s"><v>2</v></c><c r="B2" s="2"><v>1234.5</v></c><c r="C2" s="3"><v>45292</v></c></row><row r="3"><c r="A3" t="s"><v>3</v></c><c r="B3" s="2"><v>-99</v></c><c r="C3" s="4"><v>0.155</v></c></row><row r="4"><c r="A4" t="s"><v>4</v></c><c r="B4" t="inlineStr"><is><r><t xml:space="preserve">Net </t></r><r><rPr><i/></rPr><t>total</t></r></is></c><c r="C4" s="2"><f>B2+B3</f><v>1135.5</v></c></row></sheetData><conditionalFormatting sqref="B2:B3"><cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan"><formula>0</formula></cfRule></conditionalFormatting><conditionalFormatting sqref="C3:C3"><cfRule type="dataBar" priority="2"><dataBar><cfvo type="min"/><cfvo type="max"/><color rgb="FF638EC6"/></dataBar></cfRule></conditionalFormatting><drawing r:id="rId1"/></worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
